--- a/dcf/RBRK.xlsx
+++ b/dcf/RBRK.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1126,25 +1126,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>43.13482756845961</v>
+        <v>36.85688985425564</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>41.47027491738486</v>
+        <v>35.46296781305249</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>39.88468920357858</v>
+        <v>34.13496482948323</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>38.37392589086603</v>
+        <v>32.86942676816287</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>36.9340772734049</v>
+        <v>31.66309669136801</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>35.56145788751326</v>
+        <v>30.51290271899908</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>34.2525908852414</v>
+        <v>29.41594668859486</v>
       </c>
     </row>
     <row r="6">
@@ -1152,25 +1152,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>52.81662372710956</v>
+        <v>44.90152873889186</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>50.7126108583743</v>
+        <v>43.14245763884553</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>48.70940743059609</v>
+        <v>41.46745461048295</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>46.80168991977241</v>
+        <v>39.87208589323708</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>44.98444026360786</v>
+        <v>38.35217195025609</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>43.25292699008747</v>
+        <v>36.9037717693938</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>41.60268759292818</v>
+        <v>35.52316820117201</v>
       </c>
     </row>
     <row r="7">
@@ -1178,25 +1178,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>62.4984198857595</v>
+        <v>52.94616762352808</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>59.95494679936374</v>
+        <v>50.82194746463858</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>57.5341256576136</v>
+        <v>48.79994439148268</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>55.22945394867877</v>
+        <v>46.8747450183113</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>53.03480325381081</v>
+        <v>45.04124720914416</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>50.94439609266167</v>
+        <v>43.29464081978853</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>48.95278430061496</v>
+        <v>41.63038971374915</v>
       </c>
     </row>
     <row r="8">
@@ -1204,25 +1204,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>72.18021604440948</v>
+        <v>60.9908065081643</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>69.19728274035319</v>
+        <v>58.50143729043162</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>66.35884388463113</v>
+        <v>56.13243417248239</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>63.65721797758514</v>
+        <v>53.87740414338552</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>61.08516624401378</v>
+        <v>51.73032246803223</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>58.63586519523589</v>
+        <v>49.68550987018325</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>56.30288100830174</v>
+        <v>47.73761122632629</v>
       </c>
     </row>
     <row r="9">
@@ -1230,51 +1230,51 @@
         <v>7</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>81.86201220305944</v>
+        <v>69.03544539280054</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>78.43961868134262</v>
+        <v>66.18092711622468</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>75.18356211164865</v>
+        <v>63.46492395348211</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>72.08498200649151</v>
+        <v>60.88006326845974</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>69.13552923421673</v>
+        <v>58.41939772692031</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>66.3273342978101</v>
+        <v>56.07637892057798</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>63.65297771598853</v>
+        <v>53.84483273890343</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>91.54380836170938</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>87.68195462233207</v>
+      <c r="B10" s="53" t="n">
+        <v>77.08008427743675</v>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>73.86041694201772</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>84.00828033866615</v>
+        <v>70.79741373448182</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>80.51274603539788</v>
+        <v>67.88272239353395</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>77.1858922244197</v>
+        <v>65.10847298580839</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>74.0188034003843</v>
+        <v>62.4672479709727</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>71.00307442367532</v>
+        <v>59.95205425148057</v>
       </c>
     </row>
     <row r="11">
@@ -1282,25 +1282,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>101.2256045203593</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>96.92429056332151</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>92.8329985656837</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>88.94051006430426</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>85.23625521462266</v>
+        <v>85.12472316207298</v>
+      </c>
+      <c r="C11" s="53" t="n">
+        <v>81.53990676781078</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>78.12990351548154</v>
+      </c>
+      <c r="E11" s="53" t="n">
+        <v>74.88538151860816</v>
+      </c>
+      <c r="F11" s="53" t="n">
+        <v>71.79754824469646</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>81.71027250295852</v>
+        <v>68.85811702136742</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>78.35317113136209</v>
+        <v>66.05927576405772</v>
       </c>
     </row>
     <row r="13">
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>3.541306664758429</v>
+        <v>3.550231218938233</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24415,7 +24415,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24567,13 +24567,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>63.65721797758514</v>
+        <v>53.87740414338552</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>96.1274002398774</v>
+        <v>79.25348811268772</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>39.02020291661989</v>
+        <v>33.98768659133486</v>
       </c>
     </row>
     <row r="59">
